--- a/docs/Apex_HR_Master_Sitemap_and_URL_Register.xlsx
+++ b/docs/Apex_HR_Master_Sitemap_and_URL_Register.xlsx
@@ -342,8 +342,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterRoutesTable" displayName="MasterRoutesTable" ref="A4:K1091" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:K1091"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterRoutesTable" displayName="MasterRoutesTable" ref="A4:K1092" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:K1092"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Route Family"/>
@@ -409,8 +409,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DecisionRegisterTable" displayName="DecisionRegisterTable" ref="A4:G16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:G16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DecisionRegisterTable" displayName="DecisionRegisterTable" ref="A4:G17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:G17"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Decision ID"/>
     <x:tableColumn id="2" name="Decision"/>
@@ -650,7 +650,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="6" t="str">
-        <x:v>Version 1.0 • Consolidated 2 September 2026 • Canonical taxonomy: Sector</x:v>
+        <x:v>Version 1.0 • Consolidated 7 October 2026 • Canonical taxonomy: Sector</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -672,9 +672,9 @@
       <x:c r="A5" s="9" t="str">
         <x:v>Confirmed</x:v>
       </x:c>
-      <x:c r="B5" t="n">
+      <x:c r="B5">
         <x:f>COUNTIF('Master Routes'!$F$5:$F$1091,A5)</x:f>
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
         <x:v>1</x:v>
@@ -769,9 +769,9 @@
       <x:c r="A12" t="str">
         <x:v>All route records</x:v>
       </x:c>
-      <x:c r="B12" t="n">
+      <x:c r="B12">
         <x:f>COUNTA('Master Routes'!$E$5:$E$1091)</x:f>
-        <x:v>1087</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>8</x:v>
@@ -784,9 +784,9 @@
       <x:c r="A13" t="str">
         <x:v>Indexable now</x:v>
       </x:c>
-      <x:c r="B13" t="n">
+      <x:c r="B13">
         <x:f>COUNTIF('Master Routes'!$G$5:$G$1091,"Yes")</x:f>
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -36656,6 +36656,37 @@
         <x:v>Consolidate competing nested taxonomy into canonical flat service URL</x:v>
       </x:c>
     </x:row>
+    <x:row r="1092">
+      <x:c r="A1092" s="37" t="str">
+        <x:v>R1088</x:v>
+      </x:c>
+      <x:c r="B1092" s="37" t="str">
+        <x:v>Top level</x:v>
+      </x:c>
+      <x:c r="C1092" s="37" t="str"/>
+      <x:c r="D1092" s="37" t="str">
+        <x:v>Partnership</x:v>
+      </x:c>
+      <x:c r="E1092" s="37" t="str">
+        <x:v>/partnership/</x:v>
+      </x:c>
+      <x:c r="F1092" s="42" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="G1092" s="37" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H1092" s="37" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="I1092" s="37" t="str"/>
+      <x:c r="J1092" s="37" t="str">
+        <x:v>User request — 7 October 2026</x:v>
+      </x:c>
+      <x:c r="K1092" s="37" t="str">
+        <v xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">Employer partnership pricing and fractional senior HR services</v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:K1"/>
@@ -40395,6 +40426,29 @@
         <x:v>Definitions are included in the workbook</x:v>
       </x:c>
     </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="38" t="str">
+        <x:v>D-018</x:v>
+      </x:c>
+      <x:c r="B17" s="38" t="str">
+        <x:v>Partnership and pricing page</x:v>
+      </x:c>
+      <x:c r="C17" s="38" t="str">
+        <x:v>Add the explicitly approved employer partnership route /partnership/ as Confirmed and indexable; preserve supplied prices and allocations.</x:v>
+      </x:c>
+      <x:c r="D17" s="38" t="str">
+        <x:v>Resolved</x:v>
+      </x:c>
+      <x:c r="E17" s="38" t="str">
+        <x:v>2026-10-07</x:v>
+      </x:c>
+      <x:c r="F17" s="38" t="str">
+        <x:v>URL registry, employer navigation and page sitemap</x:v>
+      </x:c>
+      <x:c r="G17" s="38" t="str">
+        <x:v>Use existing Contact enquiry flow; do not introduce unapproved commercial terms.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>

--- a/docs/Apex_HR_Master_Sitemap_and_URL_Register.xlsx
+++ b/docs/Apex_HR_Master_Sitemap_and_URL_Register.xlsx
@@ -1111,10 +1111,10 @@
         <x:v>/jobs/</x:v>
       </x:c>
       <x:c r="F12" s="46" t="str">
-        <x:v>Provisional</x:v>
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="G12" s="37" t="str">
-        <x:v>Pending gate</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H12" s="37" t="str">
         <x:v>P2</x:v>
@@ -1124,7 +1124,7 @@
         <x:v>Functional Requirements Document</x:v>
       </x:c>
       <x:c r="K12" s="37" t="str">
-        <x:v>Archive route recognised; ATS source pending</x:v>
+        <x:v>Public Job Board powered by the WordPress vacancy feed; canonical Next.js route</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1142,10 +1142,10 @@
         <x:v>/jobs/[job-slug]/</x:v>
       </x:c>
       <x:c r="F13" s="46" t="str">
-        <x:v>Provisional</x:v>
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="G13" s="37" t="str">
-        <x:v>Pending gate</x:v>
+        <x:v>Open vacancies only</x:v>
       </x:c>
       <x:c r="H13" s="37" t="str">
         <x:v>P2</x:v>
@@ -1155,7 +1155,7 @@
         <x:v>Functional Requirements Document</x:v>
       </x:c>
       <x:c r="K13" s="37" t="str">
-        <x:v>Dynamic pattern; only live approved vacancies index</x:v>
+        <x:v>Only published, open, non-expired roles are indexable; WordPress front end and sitemaps disabled</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -40449,6 +40449,29 @@
         <x:v>Use existing Contact enquiry flow; do not introduce unapproved commercial terms.</x:v>
       </x:c>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="38" t="str">
+        <x:v>D-019</x:v>
+      </x:c>
+      <x:c r="B18" s="38" t="str">
+        <x:v>WordPress-powered Job Board</x:v>
+      </x:c>
+      <x:c r="C18" s="38" t="str">
+        <x:v>Confirm /jobs/ as the public Job Board and WordPress as vacancy source until ATS selection; only published, open, non-expired vacancies indexable.</x:v>
+      </x:c>
+      <x:c r="D18" s="38" t="str">
+        <x:v>Resolved</x:v>
+      </x:c>
+      <x:c r="E18" s="38" t="str">
+        <x:v>2026-10-08</x:v>
+      </x:c>
+      <x:c r="F18" s="38" t="str">
+        <x:v>WordPress vacancy CPT, Next.js routes and vacancy sitemap</x:v>
+      </x:c>
+      <x:c r="G18" s="38" t="str">
+        <x:v>WordPress vacancy pages and sitemaps disabled; applications and private CVs remain in Supabase.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
